--- a/scorecard/scorecard_data/2023/WE2023_scorecard.xlsx
+++ b/scorecard/scorecard_data/2023/WE2023_scorecard.xlsx
@@ -5,7 +5,7 @@
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1 - WE2023_Scorecard_with" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet 1 - Rounded_Poverty_and_L" sheetId="1" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="129">
   <si>
-    <t>WE2023_Scorecard_with_Poverty_and_Lack_of_Work</t>
+    <t>Rounded_Poverty_and_Lack_of_Work_Column</t>
   </si>
   <si>
     <t>State</t>
@@ -1795,7 +1795,7 @@
         <v>48.86</v>
       </c>
       <c r="G3" s="6">
-        <v>39.24</v>
+        <v>49.66</v>
       </c>
       <c r="H3" s="6">
         <v>24.64</v>
@@ -1863,7 +1863,7 @@
         <v>34.38</v>
       </c>
       <c r="G4" s="10">
-        <v>44.08</v>
+        <v>35.1</v>
       </c>
       <c r="H4" s="10">
         <v>26.57</v>
@@ -1931,7 +1931,7 @@
         <v>61.44</v>
       </c>
       <c r="G5" s="10">
-        <v>34.61</v>
+        <v>64.16</v>
       </c>
       <c r="H5" s="10">
         <v>20.51</v>
@@ -1999,7 +1999,7 @@
         <v>54.75</v>
       </c>
       <c r="G6" s="10">
-        <v>37.06</v>
+        <v>56.44</v>
       </c>
       <c r="H6" s="10">
         <v>22.76</v>
@@ -2067,7 +2067,7 @@
         <v>33.15</v>
       </c>
       <c r="G7" s="10">
-        <v>45.12</v>
+        <v>31.48</v>
       </c>
       <c r="H7" s="10">
         <v>28.87</v>
@@ -2135,7 +2135,7 @@
         <v>51.97</v>
       </c>
       <c r="G8" s="10">
-        <v>38.2</v>
+        <v>53.19</v>
       </c>
       <c r="H8" s="10">
         <v>22.52</v>
@@ -2203,7 +2203,7 @@
         <v>66.95</v>
       </c>
       <c r="G9" s="10">
-        <v>31.98</v>
+        <v>71.94</v>
       </c>
       <c r="H9" s="10">
         <v>19.9</v>
@@ -2271,7 +2271,7 @@
         <v>51.58</v>
       </c>
       <c r="G10" s="10">
-        <v>37.59</v>
+        <v>54.55</v>
       </c>
       <c r="H10" s="10">
         <v>24.2</v>
@@ -2339,7 +2339,7 @@
         <v>51.54</v>
       </c>
       <c r="G11" s="10">
-        <v>36.37</v>
+        <v>59.06</v>
       </c>
       <c r="H11" s="10">
         <v>20.45</v>
@@ -2407,7 +2407,7 @@
         <v>74.15000000000001</v>
       </c>
       <c r="G12" s="10">
-        <v>41.82</v>
+        <v>39.44</v>
       </c>
       <c r="H12" s="10">
         <v>35.2</v>
@@ -2475,7 +2475,7 @@
         <v>45.37</v>
       </c>
       <c r="G13" s="10">
-        <v>39.16</v>
+        <v>50.42</v>
       </c>
       <c r="H13" s="10">
         <v>22.43</v>
@@ -2543,7 +2543,7 @@
         <v>47.85</v>
       </c>
       <c r="G14" s="10">
-        <v>39.39</v>
+        <v>49.62</v>
       </c>
       <c r="H14" s="10">
         <v>23</v>
@@ -2611,7 +2611,7 @@
         <v>63.39</v>
       </c>
       <c r="G15" s="10">
-        <v>37.27</v>
+        <v>56.18</v>
       </c>
       <c r="H15" s="10">
         <v>21.46</v>
@@ -2679,7 +2679,7 @@
         <v>51.44</v>
       </c>
       <c r="G16" s="10">
-        <v>34.46</v>
+        <v>64.61</v>
       </c>
       <c r="H16" s="10">
         <v>20.41</v>
@@ -2747,7 +2747,7 @@
         <v>51.56</v>
       </c>
       <c r="G17" s="10">
-        <v>38.04</v>
+        <v>53.16</v>
       </c>
       <c r="H17" s="10">
         <v>24.5</v>
@@ -2815,7 +2815,7 @@
         <v>47.24</v>
       </c>
       <c r="G18" s="10">
-        <v>39.31</v>
+        <v>49.34</v>
       </c>
       <c r="H18" s="10">
         <v>25.01</v>
@@ -2883,7 +2883,7 @@
         <v>53.06</v>
       </c>
       <c r="G19" s="10">
-        <v>36.08</v>
+        <v>58.74</v>
       </c>
       <c r="H19" s="10">
         <v>25.04</v>
@@ -2951,7 +2951,7 @@
         <v>55.34</v>
       </c>
       <c r="G20" s="10">
-        <v>36.06</v>
+        <v>58.86</v>
       </c>
       <c r="H20" s="10">
         <v>24.74</v>
@@ -3019,7 +3019,7 @@
         <v>33.83</v>
       </c>
       <c r="G21" s="10">
-        <v>46.19</v>
+        <v>27.9</v>
       </c>
       <c r="H21" s="10">
         <v>30.74</v>
@@ -3087,7 +3087,7 @@
         <v>37.35</v>
       </c>
       <c r="G22" s="10">
-        <v>44.4</v>
+        <v>33.28</v>
       </c>
       <c r="H22" s="10">
         <v>29.98</v>
@@ -3155,7 +3155,7 @@
         <v>39.68</v>
       </c>
       <c r="G23" s="10">
-        <v>42.07</v>
+        <v>40.92</v>
       </c>
       <c r="H23" s="10">
         <v>26.61</v>
@@ -3223,7 +3223,7 @@
         <v>68.97</v>
       </c>
       <c r="G24" s="10">
-        <v>36.03</v>
+        <v>59.56</v>
       </c>
       <c r="H24" s="10">
         <v>22.28</v>
@@ -3291,7 +3291,7 @@
         <v>53.72</v>
       </c>
       <c r="G25" s="10">
-        <v>39.29</v>
+        <v>49.34</v>
       </c>
       <c r="H25" s="10">
         <v>25.3</v>
@@ -3359,7 +3359,7 @@
         <v>35.97</v>
       </c>
       <c r="G26" s="10">
-        <v>42.07</v>
+        <v>40.8</v>
       </c>
       <c r="H26" s="10">
         <v>27.06</v>
@@ -3427,7 +3427,7 @@
         <v>56.73</v>
       </c>
       <c r="G27" s="10">
-        <v>35.06</v>
+        <v>61.81</v>
       </c>
       <c r="H27" s="10">
         <v>24.53</v>
@@ -3495,7 +3495,7 @@
         <v>30.15</v>
       </c>
       <c r="G28" s="10">
-        <v>46</v>
+        <v>28.64</v>
       </c>
       <c r="H28" s="10">
         <v>29.94</v>
@@ -3563,7 +3563,7 @@
         <v>43.8</v>
       </c>
       <c r="G29" s="10">
-        <v>41.42</v>
+        <v>42.59</v>
       </c>
       <c r="H29" s="10">
         <v>27.4</v>
@@ -3631,7 +3631,7 @@
         <v>50.03</v>
       </c>
       <c r="G30" s="10">
-        <v>35.97</v>
+        <v>59.41</v>
       </c>
       <c r="H30" s="10">
         <v>23.62</v>
@@ -3699,7 +3699,7 @@
         <v>62.41</v>
       </c>
       <c r="G31" s="10">
-        <v>33.35</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="H31" s="10">
         <v>22.99</v>
@@ -3767,7 +3767,7 @@
         <v>58.72</v>
       </c>
       <c r="G32" s="10">
-        <v>36.12</v>
+        <v>59.46</v>
       </c>
       <c r="H32" s="10">
         <v>21.68</v>
@@ -3835,7 +3835,7 @@
         <v>57.94</v>
       </c>
       <c r="G33" s="10">
-        <v>35.42</v>
+        <v>61.81</v>
       </c>
       <c r="H33" s="10">
         <v>20.51</v>
@@ -3903,7 +3903,7 @@
         <v>61.06</v>
       </c>
       <c r="G34" s="10">
-        <v>35.6</v>
+        <v>61.49</v>
       </c>
       <c r="H34" s="10">
         <v>19.73</v>
@@ -3971,7 +3971,7 @@
         <v>35.76</v>
       </c>
       <c r="G35" s="10">
-        <v>43.05</v>
+        <v>37.44</v>
       </c>
       <c r="H35" s="10">
         <v>29.07</v>
@@ -4039,7 +4039,7 @@
         <v>45.61</v>
       </c>
       <c r="G36" s="10">
-        <v>43.49</v>
+        <v>36.22</v>
       </c>
       <c r="H36" s="10">
         <v>28.85</v>
@@ -4107,7 +4107,7 @@
         <v>42.26</v>
       </c>
       <c r="G37" s="10">
-        <v>41.16</v>
+        <v>43.96</v>
       </c>
       <c r="H37" s="10">
         <v>24.98</v>
@@ -4175,7 +4175,7 @@
         <v>73.59</v>
       </c>
       <c r="G38" s="10">
-        <v>32.22</v>
+        <v>70.22</v>
       </c>
       <c r="H38" s="10">
         <v>23.92</v>
@@ -4243,7 +4243,7 @@
         <v>42.16</v>
       </c>
       <c r="G39" s="10">
-        <v>41.38</v>
+        <v>42.52</v>
       </c>
       <c r="H39" s="10">
         <v>28.23</v>
@@ -4311,7 +4311,7 @@
         <v>48.99</v>
       </c>
       <c r="G40" s="10">
-        <v>39.64</v>
+        <v>48.12</v>
       </c>
       <c r="H40" s="10">
         <v>26.09</v>
@@ -4379,7 +4379,7 @@
         <v>48.42</v>
       </c>
       <c r="G41" s="10">
-        <v>39.06</v>
+        <v>49.66</v>
       </c>
       <c r="H41" s="10">
         <v>26.58</v>
@@ -4447,7 +4447,7 @@
         <v>44.82</v>
       </c>
       <c r="G42" s="10">
-        <v>40.42</v>
+        <v>45.78</v>
       </c>
       <c r="H42" s="10">
         <v>26.31</v>
@@ -4515,7 +4515,7 @@
         <v>51.26</v>
       </c>
       <c r="G43" s="10">
-        <v>39.17</v>
+        <v>49.68</v>
       </c>
       <c r="H43" s="10">
         <v>25.25</v>
@@ -4583,7 +4583,7 @@
         <v>42.33</v>
       </c>
       <c r="G44" s="10">
-        <v>41.63</v>
+        <v>42.6</v>
       </c>
       <c r="H44" s="10">
         <v>25</v>
@@ -4651,7 +4651,7 @@
         <v>58.51</v>
       </c>
       <c r="G45" s="10">
-        <v>34.76</v>
+        <v>62.62</v>
       </c>
       <c r="H45" s="10">
         <v>24.82</v>
@@ -4719,7 +4719,7 @@
         <v>42.28</v>
       </c>
       <c r="G46" s="10">
-        <v>42.14</v>
+        <v>40.74</v>
       </c>
       <c r="H46" s="10">
         <v>26.47</v>
@@ -4787,7 +4787,7 @@
         <v>57.2</v>
       </c>
       <c r="G47" s="10">
-        <v>35.61</v>
+        <v>60.84</v>
       </c>
       <c r="H47" s="10">
         <v>22.08</v>
@@ -4855,7 +4855,7 @@
         <v>66.64</v>
       </c>
       <c r="G48" s="10">
-        <v>30.08</v>
+        <v>78</v>
       </c>
       <c r="H48" s="10">
         <v>17.8</v>
@@ -4923,7 +4923,7 @@
         <v>37.55</v>
       </c>
       <c r="G49" s="10">
-        <v>41.58</v>
+        <v>42.2</v>
       </c>
       <c r="H49" s="10">
         <v>27.22</v>
@@ -4991,7 +4991,7 @@
         <v>60.76</v>
       </c>
       <c r="G50" s="10">
-        <v>36.28</v>
+        <v>59.26</v>
       </c>
       <c r="H50" s="10">
         <v>20.73</v>
@@ -5059,7 +5059,7 @@
         <v>64.44</v>
       </c>
       <c r="G51" s="10">
-        <v>36.54</v>
+        <v>58.04</v>
       </c>
       <c r="H51" s="10">
         <v>22.44</v>
@@ -5127,7 +5127,7 @@
         <v>28.9</v>
       </c>
       <c r="G52" s="10">
-        <v>47.58</v>
+        <v>23.84</v>
       </c>
       <c r="H52" s="10">
         <v>30.85</v>
@@ -5195,7 +5195,7 @@
         <v>52.61</v>
       </c>
       <c r="G53" s="10">
-        <v>36.74</v>
+        <v>57.15</v>
       </c>
       <c r="H53" s="10">
         <v>23.69</v>
@@ -5263,7 +5263,7 @@
         <v>57.7</v>
       </c>
       <c r="G54" s="10">
-        <v>33.78</v>
+        <v>66.34</v>
       </c>
       <c r="H54" s="10">
         <v>21.38</v>
@@ -5331,7 +5331,7 @@
         <v>3</v>
       </c>
       <c r="G55" s="10">
-        <v>59.38</v>
+        <v>2.39</v>
       </c>
       <c r="H55" s="10">
         <v>50.28</v>
